--- a/Port Distance.xlsx
+++ b/Port Distance.xlsx
@@ -1051,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ37"/>
+  <dimension ref="A2:AJ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="8.88671875" customWidth="1" style="35" min="1" max="1"/>
@@ -6779,7 +6779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F307"/>
+  <dimension ref="A1:F286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="18.77734375" bestFit="1" customWidth="1" style="37" min="1" max="1"/>
@@ -7677,593 +7677,571 @@
       <c r="F46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>KR TASMAN</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>KRTM</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="F48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="3" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="F49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="3" t="n">
-        <v>22</v>
+        <v>19.2</v>
       </c>
       <c r="F50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="3" t="n">
-        <v>23</v>
+        <v>20.4</v>
       </c>
       <c r="F51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="3" t="n">
-        <v>27</v>
+        <v>23.4</v>
       </c>
       <c r="F53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="3" t="n">
-        <v>32</v>
+        <v>24.9</v>
       </c>
       <c r="F54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="3" t="n">
-        <v>35</v>
+        <v>26.6</v>
       </c>
       <c r="F55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="3" t="n">
-        <v>38</v>
+        <v>28.4</v>
       </c>
       <c r="F56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>CUL Laemchabang</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="3" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n"/>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CUL Laemchabang</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>CULC</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
+      <c r="E58" s="3" t="n">
+        <v>32</v>
+      </c>
       <c r="F58" s="4" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CUL Laemchabang</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>CULC</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="A59" s="4" t="n"/>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
-      <c r="E59" s="3" t="n">
-        <v>17</v>
-      </c>
+      <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CUL Laemchabang</t>
+          <t>CUL HUMEN</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUHM</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>CUL Laemchabang</t>
+          <t>CUL HUMEN</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUHM</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="3" t="n">
-        <v>19.2</v>
+        <v>24.5</v>
       </c>
       <c r="F61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CUL Laemchabang</t>
+          <t>CUL HUMEN</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUHM</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="3" t="n">
-        <v>20.4</v>
+        <v>26</v>
       </c>
       <c r="F62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>CUL Laemchabang</t>
+          <t>CUL HUMEN</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUHM</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="3" t="n">
-        <v>22</v>
+        <v>27.5</v>
       </c>
       <c r="F63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>CUL Laemchabang</t>
+          <t>CUL HUMEN</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUHM</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="D64" s="4" t="n"/>
       <c r="E64" s="3" t="n">
-        <v>23.4</v>
+        <v>29</v>
       </c>
       <c r="F64" s="4" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CUL Laemchabang</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>CULC</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>14</v>
-      </c>
+      <c r="A65" s="4" t="n"/>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="3" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>CUL Laemchabang</t>
+          <t>CHANG SHENG JI 7</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CSJ</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="D66" s="4" t="n"/>
       <c r="E66" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="F66" s="4" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CUL Laemchabang</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>CULC</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E69" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="F67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CUL Laemchabang</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>CULC</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n">
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E70" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F68" s="4" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CUL Laemchabang</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>CULC</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="F69" s="4" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="n"/>
-      <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>CUL HUMEN</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>CUHM</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="F71" s="4" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>CUL HUMEN</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>CUHM</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F72" s="4" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CUL HUMEN</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>CUHM</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F73" s="4" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>CUL HUMEN</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>CUHM</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F74" s="4" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>CUL HUMEN</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>CUHM</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="F75" s="4" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="n"/>
-      <c r="B76" s="4" t="n"/>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>CHANG SHENG JI 7</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>CSJ</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79"/>
+      <c r="E77" s="5" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>CUL BANGKOK</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>CUBK</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
@@ -8276,10 +8254,10 @@
         </is>
       </c>
       <c r="C80" s="5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>15</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="81">
@@ -8294,208 +8272,208 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>15.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>17.6</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>19.6</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>21.6</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>23.8</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>25.3</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>27.8</v>
+        <v>20.06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>29.6</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>33.3</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>35.5</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>36.1</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>CUL BANGKOK</t>
+          <t>CUL NANSHA</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>CUBK</t>
+          <t>CUNS</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>38.6</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="93">
@@ -8510,10 +8488,10 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>13.84</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="94">
@@ -8528,208 +8506,208 @@
         </is>
       </c>
       <c r="C94" s="5" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>15.25</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>16.23</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>17.27</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>18.32</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>20.06</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>21.93</v>
+        <v>19.06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>23.26</v>
+        <v>20.91</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>24.64</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>26.56</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>30.15</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>32.16</v>
+        <v>29.62</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>CUL NANSHA</t>
+          <t>CUL LAEMCHABANG</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>CUNS</t>
+          <t>CULC</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>34.34</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="106">
@@ -8744,10 +8722,10 @@
         </is>
       </c>
       <c r="C106" s="5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>12.93</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="107">
@@ -8762,208 +8740,208 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>14.29</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>15.76</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>17.35</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>19.06</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>20.91</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C112" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>23.02</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>24.98</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>27.22</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>29.62</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>32.16</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>34.85</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>CUL LAEMCHABANG</t>
+          <t>CUL YANGPU</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>CULC</t>
+          <t>CUYP</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>37.7</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="119">
@@ -8978,10 +8956,10 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>13.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="120">
@@ -8996,208 +8974,208 @@
         </is>
       </c>
       <c r="C120" s="5" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>14.9</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>16.1</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>17.4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>19.2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>21.3</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>22.8</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>24.5</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>27.2</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>28.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>29.8</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>33.3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>CUL YANGPU</t>
+          <t>CUL JAKARTA</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>CUYP</t>
+          <t>CUJK</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>35.6</v>
+        <v>78</v>
       </c>
     </row>
     <row r="132">
@@ -9212,10 +9190,10 @@
         </is>
       </c>
       <c r="C132" s="5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>27.3</v>
+        <v>84</v>
       </c>
     </row>
     <row r="133">
@@ -9230,352 +9208,352 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>29.5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL MANILA</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUML</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>33</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL MANILA</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUML</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>38.2</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL MANILA</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUML</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>39.8</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL MANILA</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUML</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>42.8</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL MANILA</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUML</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>48.8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL MANILA</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUML</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL MANILA</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUML</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>85.8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL MANILA</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUML</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>78</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>84</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>CUL JAKARTA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>CUJK</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>91</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>CUL MANILA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>CUML</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>27.3</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>CUL MANILA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>CUML</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>31.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>CUL MANILA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>CUML</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>37.7</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>CUL MANILA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>CUML</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>41.7</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>CUL MANILA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>CUML</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>46</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>CUL MANILA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>CUML</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>49</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>CUL MANILA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>CUML</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>52</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>CUL MANILA</t>
+          <t>CUL KLANG</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>CUML</t>
+          <t>CUKL</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>57</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="153">
@@ -9590,208 +9568,208 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>21.2</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>23.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>28.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>30.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>32.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>34.6</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>35.2</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>36.9</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>37.6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>38.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>CUL KLANG</t>
+          <t>CUL SHEKOU</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>CUKL</t>
+          <t>CUSK</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>41.3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="165">
@@ -9806,10 +9784,10 @@
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="166">
@@ -9824,208 +9802,208 @@
         </is>
       </c>
       <c r="C166" s="5" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>21.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>25</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>26.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>28.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>30.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>33</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C174" s="5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>36</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C175" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>CUL SHEKOU</t>
+          <t>CUL HOCHIMINH</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>CUSK</t>
+          <t>CUHC</t>
         </is>
       </c>
       <c r="C177" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="178">
@@ -10040,10 +10018,10 @@
         </is>
       </c>
       <c r="C178" s="5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="179">
@@ -10058,1048 +10036,1108 @@
         </is>
       </c>
       <c r="C179" s="5" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>CUL HOCHIMINH</t>
-        </is>
-      </c>
-      <c r="B180" s="5" t="inlineStr">
-        <is>
-          <t>CUHC</t>
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>ZHI YING HE SHUN</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>ZYHS</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>21.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>CUL HOCHIMINH</t>
-        </is>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
-        <is>
-          <t>CUHC</t>
-        </is>
-      </c>
-      <c r="C181" s="5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E181" s="5" t="n">
-        <v>23</v>
-      </c>
+      <c r="A181" s="5" t="n"/>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="5" t="n"/>
+      <c r="E181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>CUL HOCHIMINH</t>
+          <t>CUL XIAMEN</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>CUHC</t>
+          <t>CUXM</t>
         </is>
       </c>
       <c r="C182" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>CUL HOCHIMINH</t>
+          <t>CUL XIAMEN</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>CUHC</t>
+          <t>CUXM</t>
         </is>
       </c>
       <c r="C183" s="5" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>26.5</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>CUL HOCHIMINH</t>
+          <t>CUL XIAMEN</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>CUHC</t>
+          <t>CUXM</t>
         </is>
       </c>
       <c r="C184" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>28.5</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>CUL HOCHIMINH</t>
+          <t>CUL XIAMEN</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>CUHC</t>
+          <t>CUXM</t>
         </is>
       </c>
       <c r="C185" s="5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>30.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>CUL HOCHIMINH</t>
+          <t>CUL XIAMEN</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>CUHC</t>
+          <t>CUXM</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>33</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>CUL HOCHIMINH</t>
+          <t>CUL XIAMEN</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>CUHC</t>
+          <t>CUXM</t>
         </is>
       </c>
       <c r="C187" s="5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>36</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>CUL HOCHIMINH</t>
+          <t>CUL XIAMEN</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>CUHC</t>
+          <t>CUXM</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>39</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>CUL HOCHIMINH</t>
+          <t>CUL XIAMEN</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>CUHC</t>
+          <t>CUXM</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>42</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>CUL HOCHIMINH</t>
+          <t>CUL XIAMEN</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>CUHC</t>
+          <t>CUXM</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>ZHI YING HE SHUN</t>
-        </is>
-      </c>
-      <c r="B191" s="6" t="inlineStr">
-        <is>
-          <t>ZYHS</t>
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>ZHONG LIAN SHAN TOU</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>ZLST</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>13.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="n"/>
-      <c r="B192" s="5" t="n"/>
-      <c r="C192" s="5" t="n"/>
-      <c r="E192" s="5" t="n"/>
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>CUL HAIPHONG</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>CUHP</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>CUL XIAMEN</t>
+          <t>CUL HAIPHONG</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>CUXM</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
-        <v>12</v>
+        <v>10.18</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>24.3</v>
+        <v>10.18</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>CUL XIAMEN</t>
+          <t>CUL HAIPHONG</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>CUXM</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
-        <v>12.5</v>
+        <v>11.63</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>24.9</v>
+        <v>11.63</v>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>CUL XIAMEN</t>
+          <t>CUL HAIPHONG</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>CUXM</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
-        <v>13</v>
+        <v>12.73</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>25.4</v>
+        <v>12.73</v>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>CUL XIAMEN</t>
+          <t>CUL HAIPHONG</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>CUXM</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
-        <v>13.5</v>
+        <v>14.14</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>26.4</v>
+        <v>14.14</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>CUL XIAMEN</t>
+          <t>CUL HAIPHONG</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>CUXM</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C197" s="5" t="n">
-        <v>14</v>
+        <v>15.76</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>27.3</v>
+        <v>15.76</v>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>CUL XIAMEN</t>
+          <t>CUL HAIPHONG</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>CUXM</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
-        <v>14.5</v>
+        <v>17.2</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>28.1</v>
+        <v>17.2</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>CUL XIAMEN</t>
+          <t>CUL HAIPHONG</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>CUXM</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C199" s="5" t="n">
-        <v>15</v>
+        <v>18.26</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>29.4</v>
+        <v>18.26</v>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>CUL XIAMEN</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>CUXM</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>30.7</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>CUL XIAMEN</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>CUXM</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>32</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>ZHONG LIAN SHAN TOU</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>ZLST</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C202" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>11.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>CUL HAIPHONG</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C203" s="5" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="F203" s="5" t="n">
-        <v>1.2</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>CUL HAIPHONG</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C204" s="5" t="n">
-        <v>10.18</v>
+        <v>14</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="F204" s="5" t="n">
-        <v>1.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>CUL HAIPHONG</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C205" s="5" t="n">
-        <v>11.63</v>
+        <v>14.5</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="F205" s="5" t="n">
-        <v>1.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>CUL HAIPHONG</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C206" s="5" t="n">
-        <v>12.73</v>
+        <v>15</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="F206" s="5" t="n">
-        <v>1.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>CUL HAIPHONG</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C207" s="5" t="n">
-        <v>14.14</v>
+        <v>15.5</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="F207" s="5" t="n">
-        <v>1.2</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>CUL HAIPHONG</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C208" s="5" t="n">
-        <v>15.76</v>
+        <v>16</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="F208" s="5" t="n">
-        <v>1.2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>CUL HAIPHONG</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C209" s="5" t="n">
-        <v>17.2</v>
+        <v>16.5</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F209" s="5" t="n">
-        <v>1.2</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>CUL HAIPHONG</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C210" s="5" t="n">
-        <v>18.26</v>
+        <v>17</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="F210" s="5" t="n">
-        <v>1.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>OSG BOSSTEC</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>OSGB</t>
         </is>
       </c>
       <c r="C211" s="5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>15.52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C212" s="5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>17.13</v>
+        <v>14</v>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C213" s="5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>18.96</v>
+        <v>14.5</v>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C214" s="5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>20.86</v>
+        <v>15.1</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C215" s="5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>22.9</v>
+        <v>15.7</v>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C216" s="5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>25.1</v>
+        <v>16.3</v>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C217" s="5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>27.44</v>
+        <v>16.8</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C218" s="5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>29.95</v>
+        <v>17.4</v>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C219" s="5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>32.63</v>
+        <v>18</v>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C220" s="5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.47</v>
+        <v>18.6</v>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C221" s="5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>38.49</v>
+        <v>19.1</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C222" s="5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>41.84</v>
+        <v>19.7</v>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>KR TASMAN</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>KRTM</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C223" s="5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>45.24</v>
+        <v>20.3</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>SINAR SOLO</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>SISO</t>
         </is>
       </c>
       <c r="C224" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>15.8</v>
+        <v>20.9</v>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>TIGER LONGKOU</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>TGLK</t>
         </is>
       </c>
       <c r="C225" s="5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>16.5</v>
+        <v>14</v>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>TIGER LONGKOU</t>
         </is>
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>TGLK</t>
         </is>
       </c>
       <c r="C226" s="5" t="n">
         <v>13</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>17.5</v>
+        <v>18</v>
+      </c>
+      <c r="F226" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>TIGER LONGKOU</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>TGLK</t>
         </is>
       </c>
       <c r="C227" s="5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>18.8</v>
+        <v>23.2</v>
+      </c>
+      <c r="F227" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>TIGER LONGKOU</t>
         </is>
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>TGLK</t>
         </is>
       </c>
       <c r="C228" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>20.2</v>
+        <v>27.3</v>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>TIGER LONGKOU</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>TGLK</t>
         </is>
       </c>
       <c r="C229" s="5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>21.5</v>
+        <v>33.5</v>
+      </c>
+      <c r="F229" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>XH DOLPHIN</t>
         </is>
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>XHDL</t>
         </is>
       </c>
       <c r="C230" s="5" t="n">
         <v>15</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>22.8</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>XH DOLPHIN</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>XHDL</t>
         </is>
       </c>
       <c r="C231" s="5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>23.5</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>XH DOLPHIN</t>
         </is>
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>XHDL</t>
         </is>
       </c>
       <c r="C232" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>24</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>XH DOLPHIN</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>XHDL</t>
         </is>
       </c>
       <c r="C233" s="5" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>24.5</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C234" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>25</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>OSG BOSSTEC</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>OSGB</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C235" s="5" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>26</v>
+        <v>9.44</v>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C236" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>14</v>
+        <v>10.61</v>
       </c>
       <c r="F236" s="5" t="n">
         <v>1.2</v>
@@ -11108,19 +11146,19 @@
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C237" s="5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>14.5</v>
+        <v>11.87</v>
       </c>
       <c r="F237" s="5" t="n">
         <v>1.2</v>
@@ -11129,19 +11167,19 @@
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C238" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>15.1</v>
+        <v>13.23</v>
       </c>
       <c r="F238" s="5" t="n">
         <v>1.2</v>
@@ -11150,19 +11188,19 @@
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C239" s="5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>15.7</v>
+        <v>14.68</v>
       </c>
       <c r="F239" s="5" t="n">
         <v>1.2</v>
@@ -11171,19 +11209,19 @@
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C240" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="F240" s="5" t="n">
         <v>1.2</v>
@@ -11192,19 +11230,19 @@
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C241" s="5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="F241" s="5" t="n">
         <v>1.2</v>
@@ -11213,19 +11251,19 @@
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C242" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>17.4</v>
+        <v>19.8</v>
       </c>
       <c r="F242" s="5" t="n">
         <v>1.2</v>
@@ -11234,19 +11272,19 @@
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C243" s="5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>18</v>
+        <v>21.8</v>
       </c>
       <c r="F243" s="5" t="n">
         <v>1.2</v>
@@ -11255,19 +11293,19 @@
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C244" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>18.6</v>
+        <v>24.4</v>
       </c>
       <c r="F244" s="5" t="n">
         <v>1.2</v>
@@ -11276,19 +11314,19 @@
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C245" s="5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>19.1</v>
+        <v>26.25</v>
       </c>
       <c r="F245" s="5" t="n">
         <v>1.2</v>
@@ -11297,19 +11335,19 @@
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>CUL HUANGPU</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>CUHP</t>
         </is>
       </c>
       <c r="C246" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>19.7</v>
+        <v>28.53</v>
       </c>
       <c r="F246" s="5" t="n">
         <v>1.2</v>
@@ -11318,1052 +11356,710 @@
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C247" s="5" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F247" s="5" t="n">
-        <v>1.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>SINAR SOLO</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>SISO</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C248" s="5" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F248" s="5" t="n">
-        <v>1.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>TIGER LONGKOU</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>TGLK</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C249" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F249" s="5" t="n">
-        <v>3</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>TIGER LONGKOU</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>TGLK</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C250" s="5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F250" s="5" t="n">
-        <v>3</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>TIGER LONGKOU</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>TGLK</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C251" s="5" t="n">
         <v>14</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="F251" s="5" t="n">
-        <v>3</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>TIGER LONGKOU</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>TGLK</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C252" s="5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="F252" s="5" t="n">
-        <v>3</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>TIGER LONGKOU</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>TGLK</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C253" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="F253" s="5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>XH DOLPHIN</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>XHDL</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C254" s="5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>37.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>XH DOLPHIN</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>XHDL</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C255" s="5" t="n">
         <v>16</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>39.4</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>XH DOLPHIN</t>
+          <t>STAR BLESSING</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>XHDL</t>
+          <t>STBL</t>
         </is>
       </c>
       <c r="C256" s="5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>44.9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>XH DOLPHIN</t>
+          <t>UGL GUANGZHOU</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>XHDL</t>
+          <t>UGLG</t>
         </is>
       </c>
       <c r="C257" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>51.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>CUL HUANGPU</t>
+          <t>UGL GUANGZHOU</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>UGLG</t>
         </is>
       </c>
       <c r="C258" s="5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F258" s="5" t="n">
-        <v>1.2</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>CUL HUANGPU</t>
+          <t>UGL GUANGZHOU</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>UGLG</t>
         </is>
       </c>
       <c r="C259" s="5" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="F259" s="5" t="n">
-        <v>1.2</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B260" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
+      <c r="A260" s="6" t="inlineStr">
+        <is>
+          <t>CUL HUMEN</t>
+        </is>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t>CUHM</t>
         </is>
       </c>
       <c r="C260" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E260" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>CUL HUMEN</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>CUHM</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="E260" s="5" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="F260" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
-        </is>
-      </c>
-      <c r="C261" s="5" t="n">
-        <v>13.5</v>
-      </c>
       <c r="E261" s="5" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="F261" s="5" t="n">
-        <v>1.2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B262" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>CUL HUMEN</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t>CUHM</t>
         </is>
       </c>
       <c r="C262" s="5" t="n">
         <v>14</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="F262" s="5" t="n">
-        <v>1.2</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B263" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t>CUL HUMEN</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t>CUHM</t>
         </is>
       </c>
       <c r="C263" s="5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>14.68</v>
-      </c>
-      <c r="F263" s="5" t="n">
-        <v>1.2</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>CUL HUANGPU</t>
+          <t>FU LIAN</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>CUHP</t>
+          <t>FULI</t>
         </is>
       </c>
       <c r="C264" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E264" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>XING DONG 88</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>XD88</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E265" s="5" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="7" t="inlineStr">
+        <is>
+          <t>XING DONG 88</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
+        <is>
+          <t>XD88</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E266" s="5" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="7" t="inlineStr">
+        <is>
+          <t>XING DONG 88</t>
+        </is>
+      </c>
+      <c r="B267" s="7" t="inlineStr">
+        <is>
+          <t>XD88</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E267" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="7" t="n"/>
+      <c r="B268" s="7" t="n"/>
+      <c r="C268" s="5" t="n"/>
+      <c r="E268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="7" t="inlineStr">
+        <is>
+          <t>KR CELEBES</t>
+        </is>
+      </c>
+      <c r="B269" s="7" t="inlineStr">
+        <is>
+          <t>KRCL</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E269" s="5" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="7" t="inlineStr">
+        <is>
+          <t>KR CELEBES</t>
+        </is>
+      </c>
+      <c r="B270" s="7" t="inlineStr">
+        <is>
+          <t>KRCL</t>
+        </is>
+      </c>
+      <c r="C270" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E270" s="0" t="n">
+        <v>9.93</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="7" t="inlineStr">
+        <is>
+          <t>KR CELEBES</t>
+        </is>
+      </c>
+      <c r="B271" s="7" t="inlineStr">
+        <is>
+          <t>KRCL</t>
+        </is>
+      </c>
+      <c r="C271" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E271" s="0" t="n">
+        <v>9.93</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="7" t="inlineStr">
+        <is>
+          <t>KR CELEBES</t>
+        </is>
+      </c>
+      <c r="B272" s="7" t="inlineStr">
+        <is>
+          <t>KRCL</t>
+        </is>
+      </c>
+      <c r="C272" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="E272" s="0" t="n">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="7" t="inlineStr">
+        <is>
+          <t>KR CELEBES</t>
+        </is>
+      </c>
+      <c r="B273" s="7" t="inlineStr">
+        <is>
+          <t>KRCL</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E273" s="5" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="7" t="inlineStr">
+        <is>
+          <t>KR CELEBES</t>
+        </is>
+      </c>
+      <c r="B274" s="7" t="inlineStr">
+        <is>
+          <t>KRCL</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E274" s="5" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="7" t="inlineStr">
+        <is>
+          <t>KR CELEBES</t>
+        </is>
+      </c>
+      <c r="B275" s="7" t="inlineStr">
+        <is>
+          <t>KRCL</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="7" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B276" s="7" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="7" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B277" s="7" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="7" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B278" s="7" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="7" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B279" s="7" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="7" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B280" s="7" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="7" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B281" s="7" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E281" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="7" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B282" s="7" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E282" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="7" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B283" s="7" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E283" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
         <v>15</v>
       </c>
-      <c r="E264" s="5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F264" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
-        </is>
-      </c>
-      <c r="C265" s="5" t="n">
+      <c r="E284" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
         <v>15.5</v>
       </c>
-      <c r="E265" s="5" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F265" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
-        </is>
-      </c>
-      <c r="C266" s="5" t="n">
+      <c r="E285" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>KR TASMAN</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>KRTM</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
         <v>16</v>
       </c>
-      <c r="E266" s="5" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F266" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
-        </is>
-      </c>
-      <c r="C267" s="5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E267" s="5" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F267" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
-        </is>
-      </c>
-      <c r="C268" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E268" s="5" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="F268" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
-        </is>
-      </c>
-      <c r="C269" s="5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="E269" s="5" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="F269" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>CUL HUANGPU</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
-        <is>
-          <t>CUHP</t>
-        </is>
-      </c>
-      <c r="C270" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E270" s="5" t="n">
-        <v>28.53</v>
-      </c>
-      <c r="F270" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C271" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E271" s="5" t="n">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B272" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C272" s="5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E272" s="5" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B273" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C273" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E273" s="5" t="n">
-        <v>18.7</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B274" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C274" s="5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E274" s="5" t="n">
-        <v>19.8</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B275" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C275" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E275" s="5" t="n">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B276" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C276" s="5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E276" s="5" t="n">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B277" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C277" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E277" s="5" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B278" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C278" s="5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="E278" s="5" t="n">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B279" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C279" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E279" s="5" t="n">
-        <v>27.4</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="5" t="inlineStr">
-        <is>
-          <t>STAR BLESSING</t>
-        </is>
-      </c>
-      <c r="B280" s="5" t="inlineStr">
-        <is>
-          <t>STBL</t>
-        </is>
-      </c>
-      <c r="C280" s="5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E280" s="5" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="5" t="inlineStr">
-        <is>
-          <t>UGL GUANGZHOU</t>
-        </is>
-      </c>
-      <c r="B281" s="5" t="inlineStr">
-        <is>
-          <t>UGLG</t>
-        </is>
-      </c>
-      <c r="C281" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E281" s="5" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="5" t="inlineStr">
-        <is>
-          <t>UGL GUANGZHOU</t>
-        </is>
-      </c>
-      <c r="B282" s="5" t="inlineStr">
-        <is>
-          <t>UGLG</t>
-        </is>
-      </c>
-      <c r="C282" s="5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E282" s="5" t="n">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="5" t="inlineStr">
-        <is>
-          <t>UGL GUANGZHOU</t>
-        </is>
-      </c>
-      <c r="B283" s="5" t="inlineStr">
-        <is>
-          <t>UGLG</t>
-        </is>
-      </c>
-      <c r="C283" s="5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="E283" s="5" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="6" t="inlineStr">
-        <is>
-          <t>CUL HUMEN</t>
-        </is>
-      </c>
-      <c r="B284" s="6" t="inlineStr">
-        <is>
-          <t>CUHM</t>
-        </is>
-      </c>
-      <c r="C284" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E284" s="5" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="6" t="inlineStr">
-        <is>
-          <t>CUL HUMEN</t>
-        </is>
-      </c>
-      <c r="B285" s="6" t="inlineStr">
-        <is>
-          <t>CUHM</t>
-        </is>
-      </c>
-      <c r="C285" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E285" s="5" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="6" t="inlineStr">
-        <is>
-          <t>CUL HUMEN</t>
-        </is>
-      </c>
-      <c r="B286" s="6" t="inlineStr">
-        <is>
-          <t>CUHM</t>
-        </is>
-      </c>
-      <c r="C286" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E286" s="5" t="n">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="6" t="inlineStr">
-        <is>
-          <t>CUL HUMEN</t>
-        </is>
-      </c>
-      <c r="B287" s="6" t="inlineStr">
-        <is>
-          <t>CUHM</t>
-        </is>
-      </c>
-      <c r="C287" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E287" s="5" t="n">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="5" t="inlineStr">
-        <is>
-          <t>FU LIAN</t>
-        </is>
-      </c>
-      <c r="B288" s="5" t="inlineStr">
-        <is>
-          <t>FULI</t>
-        </is>
-      </c>
-      <c r="C288" s="5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E288" s="5" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="6" t="inlineStr">
-        <is>
-          <t>XING DONG 88</t>
-        </is>
-      </c>
-      <c r="B289" s="6" t="inlineStr">
-        <is>
-          <t>XD88</t>
-        </is>
-      </c>
-      <c r="C289" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E289" s="5" t="n">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="7" t="inlineStr">
-        <is>
-          <t>XING DONG 88</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
-        <is>
-          <t>XD88</t>
-        </is>
-      </c>
-      <c r="C290" s="5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="E290" s="5" t="n">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="7" t="inlineStr">
-        <is>
-          <t>XING DONG 88</t>
-        </is>
-      </c>
-      <c r="B291" s="7" t="inlineStr">
-        <is>
-          <t>XD88</t>
-        </is>
-      </c>
-      <c r="C291" s="5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E291" s="5" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="7" t="n"/>
-      <c r="B292" s="7" t="n"/>
-      <c r="C292" s="5" t="n"/>
-      <c r="E292" s="5" t="n"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="7" t="inlineStr">
-        <is>
-          <t>KR CELEBES</t>
-        </is>
-      </c>
-      <c r="B293" s="7" t="inlineStr">
-        <is>
-          <t>KRCL</t>
-        </is>
-      </c>
-      <c r="C293" s="5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E293" s="5" t="n">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="7" t="inlineStr">
-        <is>
-          <t>KR CELEBES</t>
-        </is>
-      </c>
-      <c r="B294" s="7" t="inlineStr">
-        <is>
-          <t>KRCL</t>
-        </is>
-      </c>
-      <c r="C294" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="E294" s="0" t="n">
-        <v>9.93</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="7" t="inlineStr">
-        <is>
-          <t>KR CELEBES</t>
-        </is>
-      </c>
-      <c r="B295" s="7" t="inlineStr">
-        <is>
-          <t>KRCL</t>
-        </is>
-      </c>
-      <c r="C295" s="0" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E295" s="0" t="n">
-        <v>9.93</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="7" t="inlineStr">
-        <is>
-          <t>KR CELEBES</t>
-        </is>
-      </c>
-      <c r="B296" s="7" t="inlineStr">
-        <is>
-          <t>KRCL</t>
-        </is>
-      </c>
-      <c r="C296" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="E296" s="0" t="n">
-        <v>11.55</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="7" t="inlineStr">
-        <is>
-          <t>KR CELEBES</t>
-        </is>
-      </c>
-      <c r="B297" s="7" t="inlineStr">
-        <is>
-          <t>KRCL</t>
-        </is>
-      </c>
-      <c r="C297" s="5" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E297" s="5" t="n">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="7" t="inlineStr">
-        <is>
-          <t>KR CELEBES</t>
-        </is>
-      </c>
-      <c r="B298" s="7" t="inlineStr">
-        <is>
-          <t>KRCL</t>
-        </is>
-      </c>
-      <c r="C298" s="5" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="E298" s="5" t="n">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="7" t="inlineStr">
-        <is>
-          <t>KR CELEBES</t>
-        </is>
-      </c>
-      <c r="B299" s="7" t="inlineStr">
-        <is>
-          <t>KRCL</t>
-        </is>
-      </c>
-      <c r="C299" s="5" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E299" s="5" t="n">
-        <v>18.1</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="7" t="n"/>
-      <c r="B300" s="7" t="n"/>
-      <c r="C300" s="5" t="n"/>
-      <c r="E300" s="5" t="n"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="7" t="n"/>
-      <c r="B301" s="7" t="n"/>
-      <c r="C301" s="5" t="n"/>
-      <c r="E301" s="5" t="n"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="7" t="n"/>
-      <c r="B302" s="7" t="n"/>
-      <c r="C302" s="5" t="n"/>
-      <c r="E302" s="5" t="n"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="7" t="n"/>
-      <c r="B303" s="7" t="n"/>
-      <c r="C303" s="5" t="n"/>
-      <c r="E303" s="5" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="7" t="n"/>
-      <c r="B304" s="7" t="n"/>
-      <c r="C304" s="5" t="n"/>
-      <c r="E304" s="5" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="7" t="n"/>
-      <c r="B305" s="7" t="n"/>
-      <c r="C305" s="5" t="n"/>
-      <c r="E305" s="5" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="7" t="n"/>
-      <c r="B306" s="7" t="n"/>
-      <c r="C306" s="5" t="n"/>
-      <c r="E306" s="5" t="n"/>
-    </row>
-    <row r="307">
-      <c r="A307" s="7" t="n"/>
-      <c r="B307" s="7" t="n"/>
-      <c r="C307" s="5" t="n"/>
-      <c r="E307" s="5" t="n"/>
+      <c r="E286" t="n">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Port Distance.xlsx
+++ b/Port Distance.xlsx
@@ -11694,6 +11694,9 @@
       <c r="E265" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="F265" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
@@ -11712,6 +11715,9 @@
       <c r="E266" s="5" t="n">
         <v>15.5</v>
       </c>
+      <c r="F266" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
@@ -11729,6 +11735,9 @@
       </c>
       <c r="E267" s="5" t="n">
         <v>18</v>
+      </c>
+      <c r="F267" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="268">
@@ -12008,56 +12017,56 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
+      <c r="A284" s="0" t="inlineStr">
         <is>
           <t>KR TASMAN</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B284" s="0" t="inlineStr">
         <is>
           <t>KRTM</t>
         </is>
       </c>
-      <c r="C284" t="n">
+      <c r="C284" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="E284" t="n">
+      <c r="E284" s="0" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
+      <c r="A285" s="0" t="inlineStr">
         <is>
           <t>KR TASMAN</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B285" s="0" t="inlineStr">
         <is>
           <t>KRTM</t>
         </is>
       </c>
-      <c r="C285" t="n">
+      <c r="C285" s="0" t="n">
         <v>15.5</v>
       </c>
-      <c r="E285" t="n">
+      <c r="E285" s="0" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
+      <c r="A286" s="0" t="inlineStr">
         <is>
           <t>KR TASMAN</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B286" s="0" t="inlineStr">
         <is>
           <t>KRTM</t>
         </is>
       </c>
-      <c r="C286" t="n">
+      <c r="C286" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="E286" t="n">
+      <c r="E286" s="0" t="n">
         <v>42</v>
       </c>
     </row>

--- a/Port Distance.xlsx
+++ b/Port Distance.xlsx
@@ -1276,13 +1276,13 @@
       <c r="AF3" s="20" t="n"/>
       <c r="AG3" s="39" t="n"/>
       <c r="AH3" s="40" t="n">
-        <v>3641</v>
+        <v>5809.8</v>
       </c>
       <c r="AI3" s="40" t="n">
-        <v>5430</v>
+        <v>8503.450000000001</v>
       </c>
       <c r="AJ3" s="40" t="n">
-        <v>5736</v>
+        <v>9083.51</v>
       </c>
     </row>
     <row r="4" ht="15.6" customHeight="1" s="37">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>357</v>
+        <v>386.8</v>
       </c>
       <c r="C4" s="20" t="n"/>
       <c r="D4" s="20" t="n"/>
@@ -1326,13 +1326,13 @@
       <c r="AF4" s="20" t="n"/>
       <c r="AG4" s="39" t="n"/>
       <c r="AH4" s="40" t="n">
-        <v>3754</v>
+        <v>5539.6</v>
       </c>
       <c r="AI4" s="40" t="n">
-        <v>5664</v>
+        <v>8230.93</v>
       </c>
       <c r="AJ4" s="40" t="n">
-        <v>6004</v>
+        <v>8810.98</v>
       </c>
     </row>
     <row r="5" ht="15.6" customHeight="1" s="37">
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>504</v>
+        <v>462.13</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>200</v>
+        <v>146.77</v>
       </c>
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="20" t="n"/>
@@ -1378,13 +1378,13 @@
       <c r="AF5" s="20" t="n"/>
       <c r="AG5" s="39" t="n"/>
       <c r="AH5" s="40" t="n">
-        <v>3777</v>
+        <v>5386.5</v>
       </c>
       <c r="AI5" s="40" t="n">
-        <v>5720</v>
+        <v>8089.3</v>
       </c>
       <c r="AJ5" s="40" t="n">
-        <v>6071</v>
+        <v>8669.360000000001</v>
       </c>
     </row>
     <row r="6" ht="15.6" customHeight="1" s="37">
@@ -1432,7 +1432,7 @@
       <c r="AF6" s="20" t="n"/>
       <c r="AG6" s="39" t="n"/>
       <c r="AH6" s="40" t="n">
-        <v>3664</v>
+        <v>4879.1</v>
       </c>
       <c r="AI6" s="40" t="n">
         <v>5758</v>
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>1122</v>
+        <v>1153.65</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>831</v>
+        <v>858.73</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>708</v>
@@ -1488,13 +1488,13 @@
       <c r="AF7" s="20" t="n"/>
       <c r="AG7" s="39" t="n"/>
       <c r="AH7" s="40" t="n">
-        <v>3477</v>
+        <v>4761.6</v>
       </c>
       <c r="AI7" s="40" t="n">
-        <v>5641</v>
+        <v>7481.7</v>
       </c>
       <c r="AJ7" s="40" t="n">
-        <v>6093</v>
+        <v>8061.75</v>
       </c>
     </row>
     <row r="8" ht="15.6" customHeight="1" s="37">
@@ -1504,19 +1504,19 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>1150</v>
+        <v>1171.54</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>847</v>
+        <v>874.55</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>736</v>
+        <v>754.38</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>206</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>60</v>
+        <v>19.16</v>
       </c>
       <c r="G8" s="20" t="n"/>
       <c r="H8" s="20" t="n"/>
@@ -1546,13 +1546,13 @@
       <c r="AF8" s="20" t="n"/>
       <c r="AG8" s="39" t="n"/>
       <c r="AH8" s="40" t="n">
-        <v>3430</v>
+        <v>4771</v>
       </c>
       <c r="AI8" s="40" t="n">
-        <v>5595</v>
+        <v>7485.87</v>
       </c>
       <c r="AJ8" s="40" t="n">
-        <v>6049</v>
+        <v>8065.93</v>
       </c>
     </row>
     <row r="9" ht="15.6" customHeight="1" s="37">
@@ -1606,7 +1606,7 @@
       <c r="AF9" s="20" t="n"/>
       <c r="AG9" s="39" t="n"/>
       <c r="AH9" s="40" t="n">
-        <v>3431</v>
+        <v>4907.3</v>
       </c>
       <c r="AI9" s="40" t="n">
         <v>5594</v>
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>1164</v>
+        <v>1193.2</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>861</v>
+        <v>896.2</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>750</v>
+        <v>763.91</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>217</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>27</v>
+        <v>29.65</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>15</v>
@@ -1668,13 +1668,13 @@
       <c r="AF10" s="20" t="n"/>
       <c r="AG10" s="39" t="n"/>
       <c r="AH10" s="40" t="n">
-        <v>3424</v>
+        <v>4781.6</v>
       </c>
       <c r="AI10" s="40" t="n">
-        <v>5582</v>
+        <v>7497.93</v>
       </c>
       <c r="AJ10" s="40" t="n">
-        <v>6034</v>
+        <v>8077.99</v>
       </c>
     </row>
     <row r="11" ht="15.6" customHeight="1" s="37">
@@ -1732,7 +1732,7 @@
       <c r="AF11" s="20" t="n"/>
       <c r="AG11" s="39" t="n"/>
       <c r="AH11" s="40" t="n">
-        <v>3472</v>
+        <v>4766.3</v>
       </c>
       <c r="AI11" s="40" t="n">
         <v>5641</v>
@@ -1798,7 +1798,7 @@
       <c r="AF12" s="20" t="n"/>
       <c r="AG12" s="39" t="n"/>
       <c r="AH12" s="40" t="n">
-        <v>3856</v>
+        <v>5128.4</v>
       </c>
       <c r="AI12" s="40" t="n">
         <v>5907</v>
@@ -1866,7 +1866,7 @@
       <c r="AF13" s="20" t="n"/>
       <c r="AG13" s="39" t="n"/>
       <c r="AH13" s="40" t="n">
-        <v>3864</v>
+        <v>5128.4</v>
       </c>
       <c r="AI13" s="40" t="n">
         <v>5912</v>
@@ -1936,7 +1936,7 @@
       <c r="AF14" s="20" t="n"/>
       <c r="AG14" s="39" t="n"/>
       <c r="AH14" s="40" t="n">
-        <v>3811</v>
+        <v>5036</v>
       </c>
       <c r="AI14" s="40" t="n">
         <v>5888</v>
@@ -2008,7 +2008,7 @@
       <c r="AF15" s="20" t="n"/>
       <c r="AG15" s="39" t="n"/>
       <c r="AH15" s="40" t="n">
-        <v>3828</v>
+        <v>4936.2</v>
       </c>
       <c r="AI15" s="40" t="n">
         <v>5939</v>
@@ -2082,7 +2082,7 @@
       <c r="AF16" s="20" t="n"/>
       <c r="AG16" s="39" t="n"/>
       <c r="AH16" s="40" t="n">
-        <v>3284</v>
+        <v>3976</v>
       </c>
       <c r="AI16" s="40" t="n">
         <v>5652</v>
@@ -2101,7 +2101,7 @@
         <v>2497</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2191</v>
+        <v>2218.83</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>2081</v>
@@ -2158,13 +2158,13 @@
       <c r="AF17" s="20" t="n"/>
       <c r="AG17" s="39" t="n"/>
       <c r="AH17" s="40" t="n">
-        <v>2879</v>
+        <v>4141.6</v>
       </c>
       <c r="AI17" s="40" t="n">
-        <v>5253</v>
+        <v>6757.42</v>
       </c>
       <c r="AJ17" s="40" t="n">
-        <v>5834</v>
+        <v>7385.73</v>
       </c>
     </row>
     <row r="18" ht="15.6" customHeight="1" s="37">
@@ -2236,7 +2236,7 @@
       <c r="AF18" s="20" t="n"/>
       <c r="AG18" s="39" t="n"/>
       <c r="AH18" s="40" t="n">
-        <v>2840</v>
+        <v>4214.8</v>
       </c>
       <c r="AI18" s="40" t="n">
         <v>5210</v>
@@ -2316,7 +2316,7 @@
       <c r="AF19" s="20" t="n"/>
       <c r="AG19" s="39" t="n"/>
       <c r="AH19" s="40" t="n">
-        <v>2847</v>
+        <v>4198</v>
       </c>
       <c r="AI19" s="40" t="n">
         <v>5219</v>
@@ -2398,7 +2398,7 @@
       <c r="AF20" s="20" t="n"/>
       <c r="AG20" s="39" t="n"/>
       <c r="AH20" s="40" t="n">
-        <v>2848</v>
+        <v>3838</v>
       </c>
       <c r="AI20" s="40" t="n">
         <v>5220</v>
@@ -2417,7 +2417,7 @@
         <v>2461</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2161</v>
+        <v>2188.37</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>2047</v>
@@ -2456,7 +2456,7 @@
         <v>639</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>861</v>
+        <v>822.65</v>
       </c>
       <c r="Q21" s="11" t="n">
         <v>854</v>
@@ -2482,13 +2482,13 @@
       <c r="AF21" s="21" t="n"/>
       <c r="AG21" s="39" t="n"/>
       <c r="AH21" s="40" t="n">
-        <v>3415</v>
+        <v>3310.7</v>
       </c>
       <c r="AI21" s="40" t="n">
-        <v>5830</v>
+        <v>5926.6</v>
       </c>
       <c r="AJ21" s="40" t="n">
-        <v>6464</v>
+        <v>6554.92</v>
       </c>
     </row>
     <row r="22" ht="15.6" customHeight="1" s="37">
@@ -2501,7 +2501,7 @@
         <v>2676</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>2376</v>
+        <v>2403.77</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>2262</v>
@@ -2540,7 +2540,7 @@
         <v>832</v>
       </c>
       <c r="P22" s="11" t="n">
-        <v>1054</v>
+        <v>1028.34</v>
       </c>
       <c r="Q22" s="11" t="n">
         <v>1047</v>
@@ -2552,7 +2552,7 @@
         <v>1047</v>
       </c>
       <c r="T22" s="11" t="n">
-        <v>193</v>
+        <v>204.58</v>
       </c>
       <c r="U22" s="20" t="n"/>
       <c r="V22" s="20" t="n"/>
@@ -2568,13 +2568,13 @@
       <c r="AF22" s="21" t="n"/>
       <c r="AG22" s="39" t="n"/>
       <c r="AH22" s="40" t="n">
-        <v>3216</v>
+        <v>3142.9</v>
       </c>
       <c r="AI22" s="40" t="n">
-        <v>5632</v>
+        <v>5758.73</v>
       </c>
       <c r="AJ22" s="40" t="n">
-        <v>6265</v>
+        <v>6387.04</v>
       </c>
     </row>
     <row r="23" ht="15.6" customHeight="1" s="37">
@@ -2587,7 +2587,7 @@
         <v>4958</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>4658</v>
+        <v>4685.6</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>4544</v>
@@ -2626,7 +2626,7 @@
         <v>3114</v>
       </c>
       <c r="P23" s="11" t="n">
-        <v>3336</v>
+        <v>3292.52</v>
       </c>
       <c r="Q23" s="11" t="n">
         <v>3329</v>
@@ -2638,10 +2638,10 @@
         <v>3329</v>
       </c>
       <c r="T23" s="11" t="n">
-        <v>2484</v>
+        <v>2461.71</v>
       </c>
       <c r="U23" s="11" t="n">
-        <v>2303</v>
+        <v>2293.84</v>
       </c>
       <c r="V23" s="20" t="n"/>
       <c r="W23" s="20" t="n"/>
@@ -2656,13 +2656,13 @@
       <c r="AF23" s="21" t="n"/>
       <c r="AG23" s="39" t="n"/>
       <c r="AH23" s="40" t="n">
-        <v>1207</v>
+        <v>1049.09</v>
       </c>
       <c r="AI23" s="40" t="n">
-        <v>3568</v>
+        <v>4019.91</v>
       </c>
       <c r="AJ23" s="40" t="n">
-        <v>4223</v>
+        <v>4637.08</v>
       </c>
     </row>
     <row r="24" ht="15.6" customHeight="1" s="37">
@@ -2675,7 +2675,7 @@
         <v>5307</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>5007</v>
+        <v>5034.03</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>4892</v>
@@ -2714,7 +2714,7 @@
         <v>3462</v>
       </c>
       <c r="P24" s="11" t="n">
-        <v>3684</v>
+        <v>3632.62</v>
       </c>
       <c r="Q24" s="11" t="n">
         <v>3677</v>
@@ -2726,10 +2726,10 @@
         <v>3677</v>
       </c>
       <c r="T24" s="11" t="n">
-        <v>2833</v>
+        <v>2801.81</v>
       </c>
       <c r="U24" s="11" t="n">
-        <v>2652</v>
+        <v>2633.94</v>
       </c>
       <c r="V24" s="11" t="n">
         <v>454</v>
@@ -2746,13 +2746,13 @@
       <c r="AF24" s="21" t="n"/>
       <c r="AG24" s="39" t="n"/>
       <c r="AH24" s="40" t="n">
-        <v>1143</v>
+        <v>807.8</v>
       </c>
       <c r="AI24" s="40" t="n">
-        <v>3508</v>
+        <v>3914.36</v>
       </c>
       <c r="AJ24" s="40" t="n">
-        <v>4152</v>
+        <v>4502.23</v>
       </c>
     </row>
     <row r="25" ht="15.6" customHeight="1" s="37">
@@ -2762,28 +2762,28 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>6013</v>
+        <v>5994.86</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>5713</v>
+        <v>5724.76</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>5599</v>
+        <v>5571.59</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>5146</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4992</v>
+        <v>4946.75</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>4996</v>
+        <v>4956.12</v>
       </c>
       <c r="H25" s="11" t="n">
         <v>5010</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>5008</v>
+        <v>4966.68</v>
       </c>
       <c r="J25" s="11" t="n">
         <v>4975</v>
@@ -2804,7 +2804,7 @@
         <v>4169</v>
       </c>
       <c r="P25" s="11" t="n">
-        <v>4391</v>
+        <v>4326.66</v>
       </c>
       <c r="Q25" s="11" t="n">
         <v>4384</v>
@@ -2816,16 +2816,16 @@
         <v>4384</v>
       </c>
       <c r="T25" s="11" t="n">
-        <v>3540</v>
+        <v>3495.85</v>
       </c>
       <c r="U25" s="11" t="n">
-        <v>3359</v>
+        <v>3327.98</v>
       </c>
       <c r="V25" s="11" t="n">
-        <v>1220</v>
+        <v>1284.09</v>
       </c>
       <c r="W25" s="11" t="n">
-        <v>938</v>
+        <v>918.78</v>
       </c>
       <c r="X25" s="20" t="n"/>
       <c r="Y25" s="20" t="n"/>
@@ -2838,13 +2838,13 @@
       <c r="AF25" s="21" t="n"/>
       <c r="AG25" s="39" t="n"/>
       <c r="AH25" s="40" t="n">
-        <v>230</v>
+        <v>232.8</v>
       </c>
       <c r="AI25" s="40" t="n">
-        <v>2344</v>
+        <v>3960.28</v>
       </c>
       <c r="AJ25" s="40" t="n">
-        <v>3001</v>
+        <v>4540.34</v>
       </c>
     </row>
     <row r="26" ht="15.6" customHeight="1" s="37">
@@ -2932,7 +2932,7 @@
       <c r="AF26" s="21" t="n"/>
       <c r="AG26" s="39" t="n"/>
       <c r="AH26" s="40" t="n">
-        <v>1723</v>
+        <v>2190</v>
       </c>
       <c r="AI26" s="40" t="n">
         <v>2222</v>
@@ -3028,7 +3028,7 @@
       <c r="AF27" s="21" t="n"/>
       <c r="AG27" s="39" t="n"/>
       <c r="AH27" s="40" t="n">
-        <v>1887</v>
+        <v>1561</v>
       </c>
       <c r="AI27" s="40" t="n">
         <v>2286</v>
@@ -3126,7 +3126,7 @@
       <c r="AF28" s="21" t="n"/>
       <c r="AG28" s="39" t="n"/>
       <c r="AH28" s="40" t="n">
-        <v>2487</v>
+        <v>2135.7</v>
       </c>
       <c r="AI28" s="40" t="n">
         <v>2041</v>
@@ -3226,7 +3226,7 @@
       <c r="AF29" s="21" t="n"/>
       <c r="AG29" s="39" t="n"/>
       <c r="AH29" s="40" t="n">
-        <v>2439</v>
+        <v>2101.7</v>
       </c>
       <c r="AI29" s="40" t="n">
         <v>1626</v>
@@ -3245,7 +3245,7 @@
         <v>7469</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>7169</v>
+        <v>7196.56</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>7055</v>
@@ -3284,7 +3284,7 @@
         <v>5624</v>
       </c>
       <c r="P30" s="11" t="n">
-        <v>5847</v>
+        <v>5764.44</v>
       </c>
       <c r="Q30" s="11" t="n">
         <v>5840</v>
@@ -3296,19 +3296,19 @@
         <v>5840</v>
       </c>
       <c r="T30" s="11" t="n">
-        <v>4995</v>
+        <v>4933.63</v>
       </c>
       <c r="U30" s="11" t="n">
-        <v>4814</v>
+        <v>4765.75</v>
       </c>
       <c r="V30" s="11" t="n">
-        <v>2985</v>
+        <v>3015.79</v>
       </c>
       <c r="W30" s="11" t="n">
-        <v>2879</v>
+        <v>2880.94</v>
       </c>
       <c r="X30" s="11" t="n">
-        <v>2919</v>
+        <v>2925.23</v>
       </c>
       <c r="Y30" s="11" t="n">
         <v>1314</v>
@@ -3328,13 +3328,13 @@
       <c r="AF30" s="21" t="n"/>
       <c r="AG30" s="39" t="n"/>
       <c r="AH30" s="40" t="n">
-        <v>3077</v>
+        <v>2733.9</v>
       </c>
       <c r="AI30" s="40" t="n">
-        <v>1044</v>
+        <v>1060.41</v>
       </c>
       <c r="AJ30" s="40" t="n">
-        <v>1757</v>
+        <v>1635.26</v>
       </c>
     </row>
     <row r="31" ht="15.6" customHeight="1" s="37">
@@ -3432,7 +3432,7 @@
       <c r="AF31" s="21" t="n"/>
       <c r="AG31" s="39" t="n"/>
       <c r="AH31" s="40" t="n">
-        <v>3091</v>
+        <v>2747</v>
       </c>
       <c r="AI31" s="40" t="n">
         <v>1041</v>
@@ -3538,7 +3538,7 @@
       <c r="AF32" s="21" t="n"/>
       <c r="AG32" s="39" t="n"/>
       <c r="AH32" s="40" t="n">
-        <v>3342</v>
+        <v>2992.1</v>
       </c>
       <c r="AI32" s="40" t="n">
         <v>1015</v>
@@ -3646,7 +3646,7 @@
       <c r="AF33" s="39" t="n"/>
       <c r="AG33" s="39" t="n"/>
       <c r="AH33" s="40" t="n">
-        <v>3928</v>
+        <v>3622.6</v>
       </c>
       <c r="AI33" s="40" t="n">
         <v>971</v>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="AG34" s="39" t="n"/>
       <c r="AH34" s="40" t="n">
-        <v>4034</v>
+        <v>3755</v>
       </c>
       <c r="AI34" s="40" t="n">
         <v>995</v>
@@ -3772,109 +3772,109 @@
         </is>
       </c>
       <c r="B35" s="40" t="n">
-        <v>3641</v>
+        <v>5809.8</v>
       </c>
       <c r="C35" s="40" t="n">
-        <v>3754</v>
+        <v>5539.6</v>
       </c>
       <c r="D35" s="40" t="n">
-        <v>3777</v>
+        <v>5386.5</v>
       </c>
       <c r="E35" s="40" t="n">
-        <v>3664</v>
+        <v>4879.1</v>
       </c>
       <c r="F35" s="40" t="n">
-        <v>3477</v>
+        <v>4761.6</v>
       </c>
       <c r="G35" s="40" t="n">
-        <v>3430</v>
+        <v>4771</v>
       </c>
       <c r="H35" s="40" t="n">
-        <v>3431</v>
+        <v>4907.3</v>
       </c>
       <c r="I35" s="40" t="n">
-        <v>3424</v>
+        <v>4781.6</v>
       </c>
       <c r="J35" s="40" t="n">
-        <v>3472</v>
+        <v>4766.3</v>
       </c>
       <c r="K35" s="40" t="n">
-        <v>3856</v>
+        <v>5128.4</v>
       </c>
       <c r="L35" s="40" t="n">
-        <v>3864</v>
+        <v>5128.4</v>
       </c>
       <c r="M35" s="40" t="n">
-        <v>3811</v>
+        <v>5036</v>
       </c>
       <c r="N35" s="40" t="n">
-        <v>3828</v>
+        <v>4936.2</v>
       </c>
       <c r="O35" s="40" t="n">
-        <v>3284</v>
+        <v>3976</v>
       </c>
       <c r="P35" s="40" t="n">
-        <v>2879</v>
+        <v>4141.6</v>
       </c>
       <c r="Q35" s="40" t="n">
-        <v>2840</v>
+        <v>4214.8</v>
       </c>
       <c r="R35" s="40" t="n">
-        <v>2847</v>
+        <v>4198</v>
       </c>
       <c r="S35" s="40" t="n">
-        <v>2848</v>
+        <v>3838</v>
       </c>
       <c r="T35" s="40" t="n">
-        <v>3415</v>
+        <v>3310.7</v>
       </c>
       <c r="U35" s="40" t="n">
-        <v>3216</v>
+        <v>3142.9</v>
       </c>
       <c r="V35" s="40" t="n">
-        <v>1207</v>
+        <v>1049.09</v>
       </c>
       <c r="W35" s="40" t="n">
-        <v>1143</v>
+        <v>807.8</v>
       </c>
       <c r="X35" s="40" t="n">
-        <v>230</v>
+        <v>232.8</v>
       </c>
       <c r="Y35" s="40" t="n">
-        <v>1723</v>
+        <v>2190</v>
       </c>
       <c r="Z35" s="40" t="n">
-        <v>1887</v>
+        <v>1561</v>
       </c>
       <c r="AA35" s="40" t="n">
-        <v>2487</v>
+        <v>2135.7</v>
       </c>
       <c r="AB35" s="40" t="n">
-        <v>2439</v>
+        <v>2101.7</v>
       </c>
       <c r="AC35" s="40" t="n">
-        <v>3077</v>
+        <v>2733.9</v>
       </c>
       <c r="AD35" s="40" t="n">
-        <v>3091</v>
+        <v>2747</v>
       </c>
       <c r="AE35" s="40" t="n">
-        <v>3342</v>
+        <v>2992.1</v>
       </c>
       <c r="AF35" s="40" t="n">
-        <v>3928</v>
+        <v>3622.6</v>
       </c>
       <c r="AG35" s="40" t="n">
-        <v>4034</v>
+        <v>3755</v>
       </c>
       <c r="AH35" s="40" t="n">
         <v>0</v>
       </c>
       <c r="AI35" s="40" t="n">
-        <v>2416</v>
+        <v>3768.8</v>
       </c>
       <c r="AJ35" s="40" t="n">
-        <v>3068</v>
+        <v>4348.8</v>
       </c>
     </row>
     <row r="36" ht="15.6" customHeight="1" s="37">
@@ -3884,28 +3884,28 @@
         </is>
       </c>
       <c r="B36" s="40" t="n">
-        <v>5430</v>
+        <v>8503.450000000001</v>
       </c>
       <c r="C36" s="40" t="n">
-        <v>5664</v>
+        <v>8230.93</v>
       </c>
       <c r="D36" s="40" t="n">
-        <v>5720</v>
+        <v>8089.3</v>
       </c>
       <c r="E36" s="40" t="n">
         <v>5758</v>
       </c>
       <c r="F36" s="40" t="n">
-        <v>5641</v>
+        <v>7481.7</v>
       </c>
       <c r="G36" s="40" t="n">
-        <v>5595</v>
+        <v>7485.87</v>
       </c>
       <c r="H36" s="40" t="n">
         <v>5594</v>
       </c>
       <c r="I36" s="40" t="n">
-        <v>5582</v>
+        <v>7497.93</v>
       </c>
       <c r="J36" s="40" t="n">
         <v>5641</v>
@@ -3926,7 +3926,7 @@
         <v>5652</v>
       </c>
       <c r="P36" s="40" t="n">
-        <v>5253</v>
+        <v>6757.42</v>
       </c>
       <c r="Q36" s="40" t="n">
         <v>5210</v>
@@ -3938,19 +3938,19 @@
         <v>5220</v>
       </c>
       <c r="T36" s="40" t="n">
-        <v>5830</v>
+        <v>5926.6</v>
       </c>
       <c r="U36" s="40" t="n">
-        <v>5632</v>
+        <v>5758.73</v>
       </c>
       <c r="V36" s="40" t="n">
-        <v>3568</v>
+        <v>4019.91</v>
       </c>
       <c r="W36" s="40" t="n">
-        <v>3508</v>
+        <v>3914.36</v>
       </c>
       <c r="X36" s="40" t="n">
-        <v>2344</v>
+        <v>3960.28</v>
       </c>
       <c r="Y36" s="40" t="n">
         <v>2222</v>
@@ -3965,7 +3965,7 @@
         <v>1626</v>
       </c>
       <c r="AC36" s="40" t="n">
-        <v>1044</v>
+        <v>1060.41</v>
       </c>
       <c r="AD36" s="40" t="n">
         <v>1041</v>
@@ -3980,13 +3980,13 @@
         <v>995</v>
       </c>
       <c r="AH36" s="40" t="n">
-        <v>2416</v>
+        <v>3768.8</v>
       </c>
       <c r="AI36" s="40" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" s="40" t="n">
-        <v>748</v>
+        <v>766.51</v>
       </c>
     </row>
     <row r="37" ht="15.6" customHeight="1" s="37">
@@ -3996,28 +3996,28 @@
         </is>
       </c>
       <c r="B37" s="40" t="n">
-        <v>5736</v>
+        <v>9083.51</v>
       </c>
       <c r="C37" s="40" t="n">
-        <v>6004</v>
+        <v>8810.98</v>
       </c>
       <c r="D37" s="40" t="n">
-        <v>6071</v>
+        <v>8669.360000000001</v>
       </c>
       <c r="E37" s="40" t="n">
         <v>6173</v>
       </c>
       <c r="F37" s="40" t="n">
-        <v>6093</v>
+        <v>8061.75</v>
       </c>
       <c r="G37" s="40" t="n">
-        <v>6049</v>
+        <v>8065.93</v>
       </c>
       <c r="H37" s="40" t="n">
         <v>6048</v>
       </c>
       <c r="I37" s="40" t="n">
-        <v>6034</v>
+        <v>8077.99</v>
       </c>
       <c r="J37" s="40" t="n">
         <v>6095</v>
@@ -4038,7 +4038,7 @@
         <v>6223</v>
       </c>
       <c r="P37" s="40" t="n">
-        <v>5834</v>
+        <v>7385.73</v>
       </c>
       <c r="Q37" s="40" t="n">
         <v>5789</v>
@@ -4050,19 +4050,19 @@
         <v>5799</v>
       </c>
       <c r="T37" s="40" t="n">
-        <v>6464</v>
+        <v>6554.92</v>
       </c>
       <c r="U37" s="40" t="n">
-        <v>6265</v>
+        <v>6387.04</v>
       </c>
       <c r="V37" s="40" t="n">
-        <v>4223</v>
+        <v>4637.08</v>
       </c>
       <c r="W37" s="40" t="n">
-        <v>4152</v>
+        <v>4502.23</v>
       </c>
       <c r="X37" s="40" t="n">
-        <v>3001</v>
+        <v>4540.34</v>
       </c>
       <c r="Y37" s="40" t="n">
         <v>2938</v>
@@ -4077,7 +4077,7 @@
         <v>2271</v>
       </c>
       <c r="AC37" s="40" t="n">
-        <v>1757</v>
+        <v>1635.26</v>
       </c>
       <c r="AD37" s="40" t="n">
         <v>1755</v>
@@ -4092,10 +4092,10 @@
         <v>1457</v>
       </c>
       <c r="AH37" s="40" t="n">
-        <v>3068</v>
+        <v>4348.8</v>
       </c>
       <c r="AI37" s="40" t="n">
-        <v>748</v>
+        <v>766.51</v>
       </c>
       <c r="AJ37" s="40" t="n">
         <v>0</v>
@@ -8042,8 +8042,6 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
@@ -11694,7 +11692,7 @@
       <c r="E265" s="5" t="n">
         <v>12.5</v>
       </c>
-      <c r="F265" t="n">
+      <c r="F265" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -11715,7 +11713,7 @@
       <c r="E266" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="F266" t="n">
+      <c r="F266" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -11736,7 +11734,7 @@
       <c r="E267" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F267" t="n">
+      <c r="F267" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
